--- a/outputs/operations/Передача_дел_график.xlsx
+++ b/outputs/operations/Передача_дел_график.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Чек-лист приемки" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'График по дням'!$A$4:$G$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Чек-лист приемки'!$A$4:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'График по дням'!$A$4:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Чек-лист приемки'!$A$4:$E$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Последний рабочий день — 23 сентября. Розовым отмечено то, без чего работа встанет. Отмечайте «Сделано» в желтой колонке.</t>
+          <t>Последний рабочий день — 23 сентября. Главная задача — привести остатки в порядок: только вы знаете, что отгружено с июня 2025. Новому человеку передаем уже выверенный склад.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Последние переданные показания и последние оплаты</t>
+          <t>ОСТАТКИ: начать список того, что отгружено с 16.06.2025</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Открытые заказы по косметике: что оплачено и еще не отгружено</t>
+          <t>ОСТАТКИ: список отгрузок за 15 месяцев — что, сколько, кому, когда</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Заказы в пути: что едет и когда придет</t>
+          <t>Открытые заказы по косметике: что оплачено и еще не отгружено</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Сверка расчетов с поставщиками: кому должны, кто должен нам</t>
+          <t>Заказы в пути: что едет и когда придет</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Опись ключей: от каких помещений, у кого дубликаты</t>
+          <t>ОСТАТКИ: пересчет 79 позиций, дающих 80% стоимости, часть 1</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Договоры и сканы: энергоснабжение, водоснабжение, аренда</t>
+          <t>Опись ключей: от каких помещений, у кого дубликаты</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -890,16 +890,16 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>14.09 Пн</t>
+          <t>15.09 Вт</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Порядок подачи показаний по Светланской: куда и в какие числа</t>
+          <t>ОСТАТКИ: пересчет 79 позиций, часть 2</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -921,16 +921,16 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>14.09 Пн</t>
+          <t>15.09 Вт</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Лицевой счет по Аксаковской и ссылка</t>
+          <t>Порядок подачи показаний по Светланской: куда и в какие числа</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Заполнить реестр контактов: все, с кем общались за год</t>
+          <t>Лицевой счет по Аксаковской и ссылка</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Отдельно: мастер по ремонту арматуры, сварщик, электрик</t>
+          <t>Договоры и сканы: энергоснабжение, водоснабжение, аренда</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1000,9 +1000,9 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>важно</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1014,16 +1014,16 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>15.09 Вт</t>
+          <t>16.09 Ср</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Отдельно: воровайка, кран, вывоз мусора, приемка металла</t>
+          <t>ОСТАТКИ: свести пересчет и список отгрузок, объяснить расхождения</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1031,9 +1031,9 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>важно</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1045,16 +1045,16 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>15.09 Вт</t>
+          <t>16.09 Ср</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Отдельно: таможенный брокер и перевозчики по контейнерам</t>
+          <t>Сверка расчетов с поставщиками: кому должны, кто должен нам</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1076,16 +1076,16 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>16.09 Ср</t>
+          <t>17.09 Чт</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Видеообход четырех объектов: что где лежит</t>
+          <t>Заполнить реестр контактов: все, с кем общались за год</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1093,9 +1093,9 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>важно</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1107,26 +1107,26 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>16.09 Ср</t>
+          <t>17.09 Чт</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Журнал обзвона покупателей со статусами по каждой компании</t>
+          <t>Отдельно: мастер по ремонту арматуры, сварщик, электрик</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>критично</t>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>важно</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -1138,26 +1138,26 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>16.09 Ср</t>
+          <t>17.09 Чт</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Кому отправлены КП и фото, кто что просил, кто в переговорах</t>
+          <t>Отдельно: воровайка, кран, вывоз мусора, приемка металла</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>критично</t>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>важно</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1169,26 +1169,26 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>16.09 Ср</t>
+          <t>17.09 Чт</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Фотоархив оборудования</t>
+          <t>Отдельно: таможенный брокер и перевозчики по контейнерам</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>важно</t>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -1200,11 +1200,11 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>17.09 Чт</t>
+          <t>18.09 Пт</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1231,11 +1231,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>17.09 Чт</t>
+          <t>18.09 Пт</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1262,11 +1262,11 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>17.09 Чт</t>
+          <t>18.09 Пт</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1293,26 +1293,26 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>17.09 Чт</t>
+          <t>18.09 Пт</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Кто присылает прайсы и как часто они обновляются</t>
+          <t>Журнал обзвона покупателей со статусами по каждой компании</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>важно</t>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Обход Калинина вместе с новым сотрудником: счетчики, ключи, склад</t>
+          <t>Кому отправлены КП и фото, кто что просил, кто в переговорах</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>новый сотрудник</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1355,16 +1355,16 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>18.09 Пт</t>
+          <t>21.09 Пн</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+          <t>Обход Калинина вместе с новым сотрудником: счетчики, ключи, склад</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Обход Светланской, Фокино, Аксаковской: где счетчики</t>
+          <t>Показать новому, где что лежит по выверенным остаткам</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1434,9 +1434,9 @@
           <t>новый сотрудник</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>важно</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -1448,16 +1448,16 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>21.09 Пн</t>
+          <t>22.09 Вт</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Новый сотрудник сам снимает показания, вы проверяете</t>
+          <t>Обход Светланской, Фокино, Аксаковской: где счетчики</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Новый сотрудник сам оплачивает воду по четырем объектам</t>
+          <t>Новый сотрудник сам снимает показания, вы проверяете</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Совместные звонки покупателям, представить Олесю</t>
+          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый сотрудник</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1541,21 +1541,21 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>23.09 Ср</t>
+          <t>22.09 Вт</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Контрольный день: новый сотрудник работает сам, вы на связи</t>
+          <t>Совместные звонки покупателям, представить Олесю</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>новый сотрудник</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1581,74 +1581,136 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
+          <t>Новый сотрудник сам оплачивает воду по четырем объектам</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>новый сотрудник</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>23.09 Ср</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Подписать акт сверки остатков: что числится, что есть по факту</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>23.09 Ср</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
           <t>Акт приема-передачи, передача ключей</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>критично</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Всего пунктов</t>
-        </is>
-      </c>
-      <c r="D39" s="10">
-        <f>COUNTA(C5:C37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Сделано</t>
-        </is>
-      </c>
-      <c r="D40" s="10">
-        <f>COUNTIF(F5:F37,"Да")</f>
-        <v/>
-      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>критично</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Осталось критичных</t>
-        </is>
-      </c>
-      <c r="D41" s="11">
-        <f>COUNTIFS(E5:E37,"критично",F5:F37,"Нет")</f>
+          <t>Всего пунктов</t>
+        </is>
+      </c>
+      <c r="D41" s="10">
+        <f>COUNTA(C5:C39)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="C42" s="10" t="inlineStr">
         <is>
+          <t>Сделано</t>
+        </is>
+      </c>
+      <c r="D42" s="10">
+        <f>COUNTIF(F5:F39,"Да")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Осталось критичных</t>
+        </is>
+      </c>
+      <c r="D43" s="11">
+        <f>COUNTIFS(E5:E39,"критично",F5:F39,"Нет")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="10" t="inlineStr">
+        <is>
           <t>Готовность</t>
         </is>
       </c>
-      <c r="D42" s="12">
-        <f>IFERROR(D40/D39,0)</f>
+      <c r="D44" s="12">
+        <f>IFERROR(D42/D41,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G37"/>
+  <autoFilter ref="A4:G39"/>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1662,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1713,7 +1775,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Как снять показания на каждом объекте: где стоит счетчик, что записывать</t>
+          <t>Как ведется учет отгрузок: где отмечать, что продано и кому</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1729,7 +1791,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Куда и в какие числа передавать показания, по каждому объекту отдельно</t>
+          <t>Как снять показания на каждом объекте: где стоит счетчик, что записывать</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1745,7 +1807,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Как оплатить воду и свет: с какого счета, где брать квитанции</t>
+          <t>Куда и в какие числа передавать показания, по каждому объекту отдельно</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1761,7 +1823,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Как принять смену сторожа и как ему платят</t>
+          <t>Как оплатить воду и свет: с какого счета, где брать квитанции</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1777,7 +1839,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Кому звонить при аварии на каждом объекте</t>
+          <t>Как принять смену сторожа и как ему платят</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1793,7 +1855,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Порядок работы с ДЭК и Водоканалом, если в счете расхождение</t>
+          <t>Кому звонить при аварии на каждом объекте</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1809,7 +1871,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Как размещается заказ на косметику: от заявки до отгрузки</t>
+          <t>Порядок работы с ДЭК и Водоканалом, если в счете расхождение</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1825,30 +1887,46 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>Как размещается заказ на косметику: от заявки до отгрузки</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>Как проходит растаможка контейнера: кто что делает и в какие сроки</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Написано инструкций</t>
         </is>
       </c>
-      <c r="C14" s="10">
-        <f>COUNTIF(C5:C12,"Да")</f>
+      <c r="C15" s="10">
+        <f>COUNTIF(C5:C13,"Да")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1862,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1919,12 +1997,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Доступы</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Личные кабинеты ДЭК и Водоканала</t>
+          <t>Список отгрузок с 16.06.2025: что, сколько, кому, когда</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1940,12 +2018,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Доступы</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Рабочая почта</t>
+          <t>Пересчитаны 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1961,12 +2039,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Доступы</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Фарпост и другие площадки объявлений</t>
+          <t>Расхождения объяснены: продано, списано, не найдено</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1982,12 +2060,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Доступы</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Лицевые счета по четырем объектам</t>
+          <t>Акт сверки остатков подписан</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -2003,12 +2081,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Документы</t>
+          <t>Доступы</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Договоры энергоснабжения и водоснабжения</t>
+          <t>Личные кабинеты ДЭК и Водоканала</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -2024,12 +2102,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Документы</t>
+          <t>Доступы</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Договоры аренды и документы на объекты</t>
+          <t>Рабочая почта</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -2045,12 +2123,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Документы</t>
+          <t>Доступы</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Последние показания и оплаты</t>
+          <t>Фарпост и другие площадки объявлений</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -2066,12 +2144,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Деньги</t>
+          <t>Доступы</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Подотчетные средства: остаток</t>
+          <t>Лицевые счета по четырем объектам</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2087,12 +2165,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Деньги</t>
+          <t>Документы</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Сверка расчетов с поставщиками косметики</t>
+          <t>Договоры энергоснабжения и водоснабжения</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -2108,12 +2186,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Деньги</t>
+          <t>Документы</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Кому мы должны и кто должен нам</t>
+          <t>Договоры аренды и документы на объекты</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2129,12 +2207,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Ключи</t>
+          <t>Документы</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Ключи от помещений, гаража, контейнеров, будки</t>
+          <t>Последние показания и оплаты</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2150,12 +2228,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Ключи</t>
+          <t>Деньги</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Список: у кого еще есть ключи и дубликаты</t>
+          <t>Подотчетные средства: остаток</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2171,12 +2249,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Деньги</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Реестр контактов заполнен полностью</t>
+          <t>Сверка расчетов с поставщиками косметики</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2192,12 +2270,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Деньги</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Мастер по ремонту арматуры</t>
+          <t>Кому мы должны и кто должен нам</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -2213,12 +2291,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Ключи</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Подрядчики: воровайка, кран, мусор, металл, сварщик, электрик</t>
+          <t>Ключи от помещений, гаража, контейнеров, будки</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2234,12 +2312,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Ключи</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Сторожа: график и порядок оплаты</t>
+          <t>Список: у кого еще есть ключи и дубликаты</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2260,7 +2338,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Таможенный брокер и перевозчики</t>
+          <t>Реестр контактов заполнен полностью</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2276,12 +2354,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Косметика</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Открытые заказы: оплачено и не отгружено</t>
+          <t>Мастер по ремонту арматуры</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2297,12 +2375,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Косметика</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Заказы в пути</t>
+          <t>Подрядчики: воровайка, кран, мусор, металл, сварщик, электрик</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2318,12 +2396,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Косметика</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Бренды и заводы: условия, цены, минимальные партии</t>
+          <t>Сторожа: график и порядок оплаты</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2339,12 +2417,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Косметика</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Байер, консолидатор, склад в Корее</t>
+          <t>Таможенный брокер и перевозчики</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2365,7 +2443,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Сертификация: CPNP, декларации, Честный знак</t>
+          <t>Открытые заказы: оплачено и не отгружено</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2381,12 +2459,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Оборудование</t>
+          <t>Косметика</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Журнал обзвона со статусами</t>
+          <t>Заказы в пути</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2402,12 +2480,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Оборудование</t>
+          <t>Косметика</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Кому отправлены КП, кто в переговорах</t>
+          <t>Бренды и заводы: условия, цены, минимальные партии</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2423,12 +2501,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Оборудование</t>
+          <t>Косметика</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Фотоархив</t>
+          <t>Байер, консолидатор, склад в Корее</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -2444,47 +2522,131 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>Косметика</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Сертификация: CPNP, декларации, Честный знак</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Журнал обзвона со статусами</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Кому отправлены КП, кто в переговорах</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Фотоархив</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>Инструкции</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Написаны все инструкции со второго листа</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="10" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Передано пунктов</t>
         </is>
       </c>
-      <c r="D32" s="10">
-        <f>COUNTIF(D5:D30,"Да")</f>
+      <c r="D36" s="10">
+        <f>COUNTIF(D5:D34,"Да")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="C33" s="10" t="inlineStr">
+    <row r="37">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Всего пунктов</t>
         </is>
       </c>
-      <c r="D33" s="10">
-        <f>COUNTA(C5:C30)</f>
+      <c r="D37" s="10">
+        <f>COUNTA(C5:C34)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E30"/>
+  <autoFilter ref="A4:E34"/>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/operations/Передача_дел_график.xlsx
+++ b/outputs/operations/Передача_дел_график.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'График по дням'!$A$4:$G$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Чек-лист приемки'!$A$4:$E$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Чек-лист приемки'!$A$4:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Последний рабочий день — 23 сентября. Главная задача — привести остатки в порядок: только вы знаете, что отгружено с июня 2025. Новому человеку передаем уже выверенный склад.</t>
+          <t>Последний рабочий день — 23 сентября. Главная задача — пересчитать склад по факту, начиная с самого дорогого. Вспоминать, что продано за прошлые годы, не нужно: фиксируем то, что есть сейчас.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ОСТАТКИ: начать список того, что отгружено с 16.06.2025</t>
+          <t>ОСТАТКИ: начать пересчет с самых дорогих позиций</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ОСТАТКИ: список отгрузок за 15 месяцев — что, сколько, кому, когда</t>
+          <t>ОСТАТКИ: пересчет дорогих позиций, продолжение</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ОСТАТКИ: пересчет 79 позиций, дающих 80% стоимости, часть 1</t>
+          <t>ОСТАТКИ: закрыть 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>ОСТАТКИ: пересчет 79 позиций, часть 2</t>
+          <t>ОСТАТКИ: пересчет следующих по стоимости позиций</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ОСТАТКИ: свести пересчет и список отгрузок, объяснить расхождения</t>
+          <t>ОСТАТКИ: зафиксировать факт по пересчитанному, отметить непосчитанное</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Как ведется учет отгрузок: где отмечать, что продано и кому</t>
+          <t>Как дальше вести учет отгрузок: где отмечать, что продано и кому</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Список отгрузок с 16.06.2025: что, сколько, кому, когда</t>
+          <t>Пересчитаны 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Пересчитаны 79 позиций, дающих 80% стоимости</t>
+          <t>Отмечено, какие позиции пересчитаны, а какие нет</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Расхождения объяснены: продано, списано, не найдено</t>
+          <t>Акт сверки остатков подписан по пересчитанному</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Остатки</t>
+          <t>Доступы</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Акт сверки остатков подписан</t>
+          <t>Личные кабинеты ДЭК и Водоканала</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Личные кабинеты ДЭК и Водоканала</t>
+          <t>Рабочая почта</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Рабочая почта</t>
+          <t>Фарпост и другие площадки объявлений</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Фарпост и другие площадки объявлений</t>
+          <t>Лицевые счета по четырем объектам</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Доступы</t>
+          <t>Документы</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Лицевые счета по четырем объектам</t>
+          <t>Договоры энергоснабжения и водоснабжения</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Договоры энергоснабжения и водоснабжения</t>
+          <t>Договоры аренды и документы на объекты</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Договоры аренды и документы на объекты</t>
+          <t>Последние показания и оплаты</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Документы</t>
+          <t>Деньги</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Последние показания и оплаты</t>
+          <t>Подотчетные средства: остаток</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Подотчетные средства: остаток</t>
+          <t>Сверка расчетов с поставщиками косметики</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Сверка расчетов с поставщиками косметики</t>
+          <t>Кому мы должны и кто должен нам</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Деньги</t>
+          <t>Ключи</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Кому мы должны и кто должен нам</t>
+          <t>Ключи от помещений, гаража, контейнеров, будки</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Ключи от помещений, гаража, контейнеров, будки</t>
+          <t>Список: у кого еще есть ключи и дубликаты</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Ключи</t>
+          <t>Контакты</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Список: у кого еще есть ключи и дубликаты</t>
+          <t>Реестр контактов заполнен полностью</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Реестр контактов заполнен полностью</t>
+          <t>Мастер по ремонту арматуры</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Мастер по ремонту арматуры</t>
+          <t>Подрядчики: воровайка, кран, мусор, металл, сварщик, электрик</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Подрядчики: воровайка, кран, мусор, металл, сварщик, электрик</t>
+          <t>Сторожа: график и порядок оплаты</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Сторожа: график и порядок оплаты</t>
+          <t>Таможенный брокер и перевозчики</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Контакты</t>
+          <t>Косметика</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Таможенный брокер и перевозчики</t>
+          <t>Открытые заказы: оплачено и не отгружено</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Открытые заказы: оплачено и не отгружено</t>
+          <t>Заказы в пути</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Заказы в пути</t>
+          <t>Бренды и заводы: условия, цены, минимальные партии</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Бренды и заводы: условия, цены, минимальные партии</t>
+          <t>Байер, консолидатор, склад в Корее</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Байер, консолидатор, склад в Корее</t>
+          <t>Сертификация: CPNP, декларации, Честный знак</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Косметика</t>
+          <t>Оборудование</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Сертификация: CPNP, декларации, Честный знак</t>
+          <t>Журнал обзвона со статусами</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Журнал обзвона со статусами</t>
+          <t>Кому отправлены КП, кто в переговорах</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Кому отправлены КП, кто в переговорах</t>
+          <t>Фотоархив</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Оборудование</t>
+          <t>Инструкции</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Фотоархив</t>
+          <t>Написаны все инструкции со второго листа</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2600,53 +2600,32 @@
       </c>
       <c r="E33" s="8" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Инструкции</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Написаны все инструкции со второго листа</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
+    <row r="35">
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Передано пунктов</t>
+        </is>
+      </c>
+      <c r="D35" s="10">
+        <f>COUNTIF(D5:D33,"Да")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Передано пунктов</t>
+          <t>Всего пунктов</t>
         </is>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIF(D5:D34,"Да")</f>
+        <f>COUNTA(C5:C33)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Всего пунктов</t>
-        </is>
-      </c>
-      <c r="D37" s="10">
-        <f>COUNTA(C5:C34)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E34"/>
+  <autoFilter ref="A4:E33"/>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>
